--- a/data/trans_orig/P33B1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B1_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que tiene dificultad para dormirse por la noche en 2023</t>
+          <t>Población según la frecuencia con la que tiene dificultad para dormirse por la noche en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27239</t>
+          <t>28592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24256</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37927</t>
+          <t>41847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28789</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>31151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>45388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27151</t>
+          <t>27783</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71168</t>
+          <t>69320</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49692</t>
+          <t>50568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54224</t>
+          <t>55128</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106706</t>
+          <t>107755</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>309259</t>
+          <t>307020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>358741</t>
+          <t>358306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>232284</t>
+          <t>234052</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>270985</t>
+          <t>273111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>559559</t>
+          <t>556537</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>622053</t>
+          <t>618556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16521</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34025</t>
+          <t>35623</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46185</t>
+          <t>45485</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31779</t>
+          <t>31061</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>29248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>22994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52912</t>
+          <t>54244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42301</t>
+          <t>43090</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77535</t>
+          <t>76882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52458</t>
+          <t>52084</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102388</t>
+          <t>101394</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103006</t>
+          <t>103889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163545</t>
+          <t>163249</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>318913</t>
+          <t>320776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>358971</t>
+          <t>359895</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>362190</t>
+          <t>362060</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>433350</t>
+          <t>434592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>697253</t>
+          <t>699482</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>778347</t>
+          <t>779918</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35593</t>
+          <t>35838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22064</t>
+          <t>21038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38893</t>
+          <t>39085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41198</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68529</t>
+          <t>69490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42830</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25727</t>
+          <t>25276</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44376</t>
+          <t>43944</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50674</t>
+          <t>49846</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>80307</t>
+          <t>79626</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65520</t>
+          <t>65306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100255</t>
+          <t>98726</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107695</t>
+          <t>107922</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138778</t>
+          <t>139230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>179823</t>
+          <t>183224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226007</t>
+          <t>228580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381919</t>
+          <t>382998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421917</t>
+          <t>422097</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>338315</t>
+          <t>339011</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>372755</t>
+          <t>374475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>730691</t>
+          <t>730384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>786110</t>
+          <t>787175</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61079</t>
+          <t>59613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50633</t>
+          <t>49845</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75704</t>
+          <t>76704</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>63767</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>128123</t>
+          <t>129110</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20343</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70554</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57605</t>
+          <t>57837</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84819</t>
+          <t>85081</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69281</t>
+          <t>73231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146099</t>
+          <t>148046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55928</t>
+          <t>52310</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>180651</t>
+          <t>182073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>131749</t>
+          <t>131709</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>175723</t>
+          <t>176205</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>162693</t>
+          <t>177189</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>339568</t>
+          <t>343830</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>588971</t>
+          <t>588090</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>793919</t>
+          <t>793818</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>396618</t>
+          <t>396621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>466580</t>
+          <t>472775</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>997993</t>
+          <t>996831</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1309800</t>
+          <t>1280574</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>41416</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67691</t>
+          <t>66185</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>72302</t>
+          <t>72159</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98282</t>
+          <t>97654</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>119914</t>
+          <t>118763</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>156995</t>
+          <t>157450</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29479</t>
+          <t>29245</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68313</t>
+          <t>68717</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92636</t>
+          <t>93017</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>103140</t>
+          <t>103807</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>137456</t>
+          <t>138038</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124071</t>
+          <t>124514</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>163134</t>
+          <t>163231</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>137848</t>
+          <t>137742</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167998</t>
+          <t>167772</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>268806</t>
+          <t>271891</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>317159</t>
+          <t>317706</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>302462</t>
+          <t>303529</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>347385</t>
+          <t>346328</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>212839</t>
+          <t>209683</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>248334</t>
+          <t>245959</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>524536</t>
+          <t>527293</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>583713</t>
+          <t>582259</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32234</t>
+          <t>31678</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49241</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>25137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>103002</t>
+          <t>103395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>55220</t>
+          <t>54545</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>140821</t>
+          <t>138904</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>36461</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21228</t>
+          <t>20548</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>80262</t>
+          <t>79859</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>36722</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>101802</t>
+          <t>101843</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>86292</t>
+          <t>84996</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>112301</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>55062</t>
+          <t>50217</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>199239</t>
+          <t>198589</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>122039</t>
+          <t>119804</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>294127</t>
+          <t>294124</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>186401</t>
+          <t>186581</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>217575</t>
+          <t>217318</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>234233</t>
+          <t>235234</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>503870</t>
+          <t>509868</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>450525</t>
+          <t>452161</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>752835</t>
+          <t>763360</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>33000</t>
+          <t>33710</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>51342</t>
+          <t>52200</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>77856</t>
+          <t>76599</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>102763</t>
+          <t>101158</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>116519</t>
+          <t>117090</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>146883</t>
+          <t>148309</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24351</t>
+          <t>24656</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>41104</t>
+          <t>40194</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>62404</t>
+          <t>62186</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>84301</t>
+          <t>83510</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>91275</t>
+          <t>92921</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>119219</t>
+          <t>120800</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>62858</t>
+          <t>63135</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>85757</t>
+          <t>85038</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>120340</t>
+          <t>119366</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>145799</t>
+          <t>145028</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>189412</t>
+          <t>186573</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>224271</t>
+          <t>222547</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>122020</t>
+          <t>122539</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>147068</t>
+          <t>147629</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>118428</t>
+          <t>117246</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>145498</t>
+          <t>144144</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>245599</t>
+          <t>245213</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>286015</t>
+          <t>285781</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>172956</t>
+          <t>168068</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>250616</t>
+          <t>249579</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>295852</t>
+          <t>293250</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>400890</t>
+          <t>403360</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>504513</t>
+          <t>503996</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>631272</t>
+          <t>634570</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>156975</t>
+          <t>159525</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>235374</t>
+          <t>235524</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>279624</t>
+          <t>279869</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>377380</t>
+          <t>381421</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>472990</t>
+          <t>467339</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>595723</t>
+          <t>594319</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>476973</t>
+          <t>473725</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>687423</t>
+          <t>687018</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>638320</t>
+          <t>665901</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>874498</t>
+          <t>877771</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1242481</t>
+          <t>1231754</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1527666</t>
+          <t>1532344</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2323366</t>
+          <t>2317871</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2677144</t>
+          <t>2670482</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2027298</t>
+          <t>2020954</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2480848</t>
+          <t>2453799</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4407633</t>
+          <t>4389629</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4928401</t>
+          <t>4883507</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B1_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28592</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>31400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>22297</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7701</t>
+          <t>10483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41847</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26200</t>
+          <t>25166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,67 +873,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31151</t>
+          <t>33781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>30371</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>17139</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>49322</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>2,22%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>9,95%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>25874</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>13639</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>45388</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43686</t>
+          <t>41616</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27783</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69320</t>
+          <t>63858</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>44777</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50568</t>
+          <t>62898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>76611</t>
+          <t>86393</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55128</t>
+          <t>63086</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107755</t>
+          <t>118174</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>337158</t>
+          <t>347588</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>307020</t>
+          <t>321281</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>358306</t>
+          <t>367177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>254620</t>
+          <t>283657</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>234052</t>
+          <t>260238</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>273111</t>
+          <t>304999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>591778</t>
+          <t>631245</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>556537</t>
+          <t>597503</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>618556</t>
+          <t>660788</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>20936</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35623</t>
+          <t>35937</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>33655</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>45485</t>
+          <t>46354</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31061</t>
+          <t>28929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18732</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>31820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>35846</t>
+          <t>36483</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>25251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54244</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58081</t>
+          <t>74223</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43090</t>
+          <t>55585</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76882</t>
+          <t>96219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79660</t>
+          <t>90374</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52084</t>
+          <t>72091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101394</t>
+          <t>109532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>137740</t>
+          <t>164597</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103889</t>
+          <t>139574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163249</t>
+          <t>194447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>340192</t>
+          <t>376082</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>320776</t>
+          <t>352702</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>359895</t>
+          <t>397455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>390643</t>
+          <t>367156</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>362060</t>
+          <t>345803</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>434592</t>
+          <t>386465</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>730834</t>
+          <t>743238</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>699482</t>
+          <t>708621</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>779918</t>
+          <t>771282</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>26219</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15257</t>
+          <t>16975</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35838</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29719</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21038</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>44267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>53926</t>
+          <t>59159</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42351</t>
+          <t>45878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69490</t>
+          <t>74129</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29471</t>
+          <t>31214</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41624</t>
+          <t>46860</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33661</t>
+          <t>40873</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25276</t>
+          <t>31679</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43944</t>
+          <t>52402</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,22 +2046,22 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>63132</t>
+          <t>72086</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>49846</t>
+          <t>57403</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79626</t>
+          <t>90961</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>80570</t>
+          <t>92142</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65306</t>
+          <t>75714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98726</t>
+          <t>111633</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>123164</t>
+          <t>140886</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107922</t>
+          <t>123406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139230</t>
+          <t>159387</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>203734</t>
+          <t>233028</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183224</t>
+          <t>208473</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228580</t>
+          <t>261391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>402090</t>
+          <t>471262</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>382998</t>
+          <t>446168</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422097</t>
+          <t>493586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>355924</t>
+          <t>407441</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>339011</t>
+          <t>387471</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>374475</t>
+          <t>427722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>758014</t>
+          <t>878703</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>730384</t>
+          <t>847484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>787175</t>
+          <t>910115</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>43114</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>30218</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59613</t>
+          <t>58255</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62441</t>
+          <t>70031</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49845</t>
+          <t>57087</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76704</t>
+          <t>83595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>101244</t>
+          <t>113145</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63767</t>
+          <t>94525</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>129110</t>
+          <t>133002</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>45096</t>
+          <t>48381</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70466</t>
+          <t>64363</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>71479</t>
+          <t>77798</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57837</t>
+          <t>65186</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85081</t>
+          <t>90984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>116575</t>
+          <t>126179</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73231</t>
+          <t>108085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148046</t>
+          <t>145648</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>123557</t>
+          <t>136091</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52310</t>
+          <t>115628</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>182073</t>
+          <t>157604</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>156651</t>
+          <t>172623</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>131709</t>
+          <t>155328</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>176205</t>
+          <t>190340</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>280209</t>
+          <t>308714</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>177189</t>
+          <t>281192</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>343830</t>
+          <t>338020</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>680330</t>
+          <t>473031</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>588090</t>
+          <t>444925</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>793818</t>
+          <t>497886</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>421927</t>
+          <t>416043</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>396621</t>
+          <t>394547</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>472775</t>
+          <t>436744</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1102258</t>
+          <t>889074</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>996831</t>
+          <t>854394</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1280574</t>
+          <t>920698</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>64,07%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>53356</t>
+          <t>56578</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41416</t>
+          <t>44605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66185</t>
+          <t>71160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>84604</t>
+          <t>97205</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>72159</t>
+          <t>83681</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>97654</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>137960</t>
+          <t>153783</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>118763</t>
+          <t>135972</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>157450</t>
+          <t>176744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>39375</t>
+          <t>41280</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29245</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51571</t>
+          <t>54369</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>79787</t>
+          <t>90097</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68717</t>
+          <t>77391</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93017</t>
+          <t>104294</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>119162</t>
+          <t>131376</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>103807</t>
+          <t>113456</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138038</t>
+          <t>150701</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>142252</t>
+          <t>156239</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124514</t>
+          <t>136537</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>163231</t>
+          <t>178171</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>151691</t>
+          <t>166911</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>137742</t>
+          <t>150471</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167772</t>
+          <t>185075</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>293943</t>
+          <t>323149</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>271891</t>
+          <t>295525</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>317706</t>
+          <t>351282</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>325221</t>
+          <t>354168</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>303529</t>
+          <t>331481</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>346328</t>
+          <t>377639</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>228981</t>
+          <t>253382</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>209683</t>
+          <t>233072</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>245959</t>
+          <t>272695</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>554202</t>
+          <t>607549</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>527293</t>
+          <t>577867</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>582259</t>
+          <t>637248</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>40363</t>
+          <t>45061</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31678</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>56342</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>65226</t>
+          <t>72960</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>62006</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>103395</t>
+          <t>84255</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>105589</t>
+          <t>118021</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>54545</t>
+          <t>103100</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>138904</t>
+          <t>134367</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19992</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36461</t>
+          <t>41123</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>50110</t>
+          <t>54651</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20548</t>
+          <t>44632</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>79859</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>77010</t>
+          <t>84590</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36722</t>
+          <t>71865</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>101843</t>
+          <t>98208</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>98796</t>
+          <t>108366</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>84996</t>
+          <t>94429</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>112301</t>
+          <t>123105</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>127236</t>
+          <t>137328</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>50217</t>
+          <t>124043</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>198589</t>
+          <t>153542</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>226033</t>
+          <t>245694</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>119804</t>
+          <t>226502</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>294124</t>
+          <t>267722</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>202106</t>
+          <t>223713</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>186581</t>
+          <t>207799</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>217318</t>
+          <t>240748</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>365230</t>
+          <t>173660</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>235234</t>
+          <t>158173</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>509868</t>
+          <t>188035</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>567336</t>
+          <t>397372</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>452161</t>
+          <t>373756</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>763360</t>
+          <t>419904</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>607802</t>
+          <t>438598</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>975968</t>
+          <t>845677</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>975968</t>
+          <t>845677</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>975968</t>
+          <t>845677</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>47347</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>33710</t>
+          <t>37990</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>52200</t>
+          <t>59449</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>88959</t>
+          <t>99986</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>76599</t>
+          <t>86365</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>101158</t>
+          <t>114386</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>131402</t>
+          <t>147333</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>117090</t>
+          <t>129709</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>148309</t>
+          <t>165431</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>31813</t>
+          <t>35039</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24656</t>
+          <t>26645</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40194</t>
+          <t>44942</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>73216</t>
+          <t>79822</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>62186</t>
+          <t>69641</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>83510</t>
+          <t>92110</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,17 +4322,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>105029</t>
+          <t>114861</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>92921</t>
+          <t>101509</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>120800</t>
+          <t>130838</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>74118</t>
+          <t>82053</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>63135</t>
+          <t>69669</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>85038</t>
+          <t>96285</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>132841</t>
+          <t>141541</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>119366</t>
+          <t>128894</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>145028</t>
+          <t>154440</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>206959</t>
+          <t>223594</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>186573</t>
+          <t>203392</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>222547</t>
+          <t>242266</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>134384</t>
+          <t>145759</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>122539</t>
+          <t>130576</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>147629</t>
+          <t>161072</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>130815</t>
+          <t>143260</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>117246</t>
+          <t>129137</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>144144</t>
+          <t>158176</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>265199</t>
+          <t>289019</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>245213</t>
+          <t>268927</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>285781</t>
+          <t>310301</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>215365</t>
+          <t>235280</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>204381</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>249579</t>
+          <t>265608</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>364310</t>
+          <t>412114</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>293250</t>
+          <t>378483</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>403360</t>
+          <t>446216</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>579675</t>
+          <t>647393</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>503996</t>
+          <t>604744</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>634570</t>
+          <t>696240</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>200879</t>
+          <t>214067</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>159525</t>
+          <t>187792</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>235524</t>
+          <t>246156</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>341750</t>
+          <t>381879</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>279869</t>
+          <t>351845</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>381421</t>
+          <t>411565</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>542628</t>
+          <t>595947</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>467339</t>
+          <t>551476</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>594319</t>
+          <t>640959</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>621062</t>
+          <t>690730</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>473725</t>
+          <t>646410</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>687018</t>
+          <t>746665</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>804167</t>
+          <t>894439</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>665901</t>
+          <t>852398</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>877771</t>
+          <t>938218</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1425229</t>
+          <t>1585169</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1231754</t>
+          <t>1519010</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1532344</t>
+          <t>1652378</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2421482</t>
+          <t>2391603</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2317871</t>
+          <t>2335211</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2670482</t>
+          <t>2447533</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2148139</t>
+          <t>2044599</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2020954</t>
+          <t>1994367</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2453799</t>
+          <t>2098085</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4569622</t>
+          <t>4436201</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4389629</t>
+          <t>4357154</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4883507</t>
+          <t>4515442</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
